--- a/labs/5.lab/table.xlsx
+++ b/labs/5.lab/table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rod/Documents/ehu/dt/labs/5.lab/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B3DE27-28F8-C345-96AD-9AD581A99B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96867A7A-A5FD-684A-A5CD-F7746838DB43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{82360F73-6F90-EA4F-9988-258125F9AD17}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="21900" xr2:uid="{82360F73-6F90-EA4F-9988-258125F9AD17}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -571,17 +571,17 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1151,11 +1151,11 @@
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
@@ -1167,37 +1167,37 @@
       <c r="C13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="18"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="18"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="18"/>
     </row>
     <row r="15" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
@@ -1209,18 +1209,18 @@
       <c r="C15" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="18"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="19"/>
-      <c r="O15" s="19"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="18"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="18"/>
       <c r="P15" s="15"/>
       <c r="Q15" s="15"/>
       <c r="R15" s="15"/>
@@ -1230,7 +1230,7 @@
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="16" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -1239,18 +1239,18 @@
       <c r="C16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="18"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="18"/>
       <c r="P16" s="15"/>
       <c r="Q16" s="15"/>
       <c r="R16" s="15"/>
@@ -1267,18 +1267,18 @@
       <c r="C17" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="18"/>
       <c r="P17" s="15"/>
       <c r="Q17" s="15"/>
       <c r="R17" s="15"/>
@@ -1312,18 +1312,18 @@
       <c r="C18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="18"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="18"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="18"/>
       <c r="P18" s="15"/>
       <c r="Q18" s="15"/>
       <c r="R18" s="15"/>
@@ -1348,23 +1348,23 @@
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="18"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
       <c r="P19" s="15"/>
       <c r="Q19" s="15"/>
       <c r="R19" s="15"/>
@@ -1445,20 +1445,20 @@
       <c r="C21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="18"/>
       <c r="P21" s="15"/>
       <c r="Q21" s="15"/>
       <c r="R21" s="15"/>
@@ -1492,18 +1492,18 @@
       <c r="C22" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="18"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="18"/>
       <c r="P22" s="15"/>
       <c r="Q22" s="15"/>
       <c r="R22" s="15"/>
@@ -1519,18 +1519,18 @@
       <c r="C23" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D23" s="18"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="18"/>
       <c r="P23" s="15"/>
       <c r="Q23" s="15"/>
       <c r="R23" s="15"/>
@@ -1540,23 +1540,23 @@
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="18"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="18"/>
       <c r="P24" s="15"/>
       <c r="Q24" s="15"/>
       <c r="R24" s="15"/>
@@ -1573,20 +1573,20 @@
       <c r="C25" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
       <c r="P25" s="15"/>
       <c r="Q25" s="15"/>
       <c r="R25" s="15"/>
@@ -1623,21 +1623,21 @@
       <c r="C26" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="19"/>
-      <c r="O26" s="19"/>
-      <c r="P26" s="19"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="18"/>
+      <c r="P26" s="18"/>
       <c r="Q26" s="15"/>
       <c r="R26" s="15"/>
       <c r="S26" s="15"/>
@@ -1673,18 +1673,18 @@
       <c r="C27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D27" s="18"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="19"/>
-      <c r="O27" s="19"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
+      <c r="M27" s="18"/>
+      <c r="N27" s="18"/>
+      <c r="O27" s="18"/>
       <c r="P27" s="15"/>
       <c r="Q27" s="15"/>
       <c r="R27" s="15"/>
@@ -1721,18 +1721,18 @@
       <c r="C28" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D28" s="18"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18"/>
+      <c r="N28" s="18"/>
+      <c r="O28" s="18"/>
       <c r="P28" s="15"/>
       <c r="Q28" s="15"/>
       <c r="R28" s="15"/>
@@ -2202,13 +2202,9 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="D24:O24"/>
-    <mergeCell ref="D25:O25"/>
-    <mergeCell ref="D27:O27"/>
-    <mergeCell ref="D28:O28"/>
-    <mergeCell ref="D13:O13"/>
-    <mergeCell ref="D14:O14"/>
-    <mergeCell ref="D26:P26"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A19:C19"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="D15:O15"/>
     <mergeCell ref="D16:O16"/>
@@ -2219,9 +2215,13 @@
     <mergeCell ref="D21:O21"/>
     <mergeCell ref="D22:O22"/>
     <mergeCell ref="D23:O23"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D24:O24"/>
+    <mergeCell ref="D25:O25"/>
+    <mergeCell ref="D27:O27"/>
+    <mergeCell ref="D28:O28"/>
+    <mergeCell ref="D13:O13"/>
+    <mergeCell ref="D14:O14"/>
+    <mergeCell ref="D26:P26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/labs/5.lab/table.xlsx
+++ b/labs/5.lab/table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rod/Documents/ehu/dt/labs/5.lab/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96867A7A-A5FD-684A-A5CD-F7746838DB43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F187AEF3-F900-EA4A-98D4-BE3081908AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="21900" xr2:uid="{82360F73-6F90-EA4F-9988-258125F9AD17}"/>
   </bookViews>
@@ -574,14 +574,14 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1151,11 +1151,11 @@
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
@@ -1167,37 +1167,37 @@
       <c r="C13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="18"/>
-      <c r="L13" s="18"/>
-      <c r="M13" s="18"/>
-      <c r="N13" s="18"/>
-      <c r="O13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="18"/>
-      <c r="N14" s="18"/>
-      <c r="O14" s="18"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
     </row>
     <row r="15" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
@@ -1209,18 +1209,18 @@
       <c r="C15" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="17"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="18"/>
-      <c r="M15" s="18"/>
-      <c r="N15" s="18"/>
-      <c r="O15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="19"/>
       <c r="P15" s="15"/>
       <c r="Q15" s="15"/>
       <c r="R15" s="15"/>
@@ -1239,18 +1239,18 @@
       <c r="C16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="17"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="18"/>
-      <c r="M16" s="18"/>
-      <c r="N16" s="18"/>
-      <c r="O16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
       <c r="P16" s="15"/>
       <c r="Q16" s="15"/>
       <c r="R16" s="15"/>
@@ -1267,18 +1267,18 @@
       <c r="C17" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="18"/>
-      <c r="N17" s="18"/>
-      <c r="O17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="19"/>
       <c r="P17" s="15"/>
       <c r="Q17" s="15"/>
       <c r="R17" s="15"/>
@@ -1312,18 +1312,18 @@
       <c r="C18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="17"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
-      <c r="M18" s="18"/>
-      <c r="N18" s="18"/>
-      <c r="O18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
       <c r="P18" s="15"/>
       <c r="Q18" s="15"/>
       <c r="R18" s="15"/>
@@ -1348,23 +1348,23 @@
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="18"/>
-      <c r="L19" s="18"/>
-      <c r="M19" s="18"/>
-      <c r="N19" s="18"/>
-      <c r="O19" s="18"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
       <c r="P19" s="15"/>
       <c r="Q19" s="15"/>
       <c r="R19" s="15"/>
@@ -1445,20 +1445,20 @@
       <c r="C21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="18"/>
-      <c r="K21" s="18"/>
-      <c r="L21" s="18"/>
-      <c r="M21" s="18"/>
-      <c r="N21" s="18"/>
-      <c r="O21" s="18"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
       <c r="P21" s="15"/>
       <c r="Q21" s="15"/>
       <c r="R21" s="15"/>
@@ -1492,18 +1492,18 @@
       <c r="C22" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="18"/>
-      <c r="K22" s="18"/>
-      <c r="L22" s="18"/>
-      <c r="M22" s="18"/>
-      <c r="N22" s="18"/>
-      <c r="O22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19"/>
       <c r="P22" s="15"/>
       <c r="Q22" s="15"/>
       <c r="R22" s="15"/>
@@ -1519,18 +1519,18 @@
       <c r="C23" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D23" s="17"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="18"/>
-      <c r="K23" s="18"/>
-      <c r="L23" s="18"/>
-      <c r="M23" s="18"/>
-      <c r="N23" s="18"/>
-      <c r="O23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
       <c r="P23" s="15"/>
       <c r="Q23" s="15"/>
       <c r="R23" s="15"/>
@@ -1540,23 +1540,23 @@
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="18"/>
-      <c r="K24" s="18"/>
-      <c r="L24" s="18"/>
-      <c r="M24" s="18"/>
-      <c r="N24" s="18"/>
-      <c r="O24" s="18"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
       <c r="P24" s="15"/>
       <c r="Q24" s="15"/>
       <c r="R24" s="15"/>
@@ -1573,20 +1573,20 @@
       <c r="C25" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="18"/>
-      <c r="K25" s="18"/>
-      <c r="L25" s="18"/>
-      <c r="M25" s="18"/>
-      <c r="N25" s="18"/>
-      <c r="O25" s="18"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
       <c r="P25" s="15"/>
       <c r="Q25" s="15"/>
       <c r="R25" s="15"/>
@@ -1623,21 +1623,21 @@
       <c r="C26" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="18"/>
-      <c r="K26" s="18"/>
-      <c r="L26" s="18"/>
-      <c r="M26" s="18"/>
-      <c r="N26" s="18"/>
-      <c r="O26" s="18"/>
-      <c r="P26" s="18"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
       <c r="Q26" s="15"/>
       <c r="R26" s="15"/>
       <c r="S26" s="15"/>
@@ -1673,18 +1673,18 @@
       <c r="C27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D27" s="17"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="18"/>
-      <c r="K27" s="18"/>
-      <c r="L27" s="18"/>
-      <c r="M27" s="18"/>
-      <c r="N27" s="18"/>
-      <c r="O27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
       <c r="P27" s="15"/>
       <c r="Q27" s="15"/>
       <c r="R27" s="15"/>
@@ -1721,18 +1721,18 @@
       <c r="C28" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D28" s="17"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="18"/>
-      <c r="K28" s="18"/>
-      <c r="L28" s="18"/>
-      <c r="M28" s="18"/>
-      <c r="N28" s="18"/>
-      <c r="O28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
       <c r="P28" s="15"/>
       <c r="Q28" s="15"/>
       <c r="R28" s="15"/>
@@ -2202,6 +2202,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="D25:O25"/>
+    <mergeCell ref="D27:O27"/>
+    <mergeCell ref="D28:O28"/>
+    <mergeCell ref="D13:O13"/>
+    <mergeCell ref="D14:O14"/>
+    <mergeCell ref="D26:P26"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A19:C19"/>
@@ -2216,12 +2222,6 @@
     <mergeCell ref="D22:O22"/>
     <mergeCell ref="D23:O23"/>
     <mergeCell ref="D24:O24"/>
-    <mergeCell ref="D25:O25"/>
-    <mergeCell ref="D27:O27"/>
-    <mergeCell ref="D28:O28"/>
-    <mergeCell ref="D13:O13"/>
-    <mergeCell ref="D14:O14"/>
-    <mergeCell ref="D26:P26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
